--- a/output_data/output.xlsx
+++ b/output_data/output.xlsx
@@ -414,76 +414,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>https://www.loudsound.ru/catalog/shirokopolosniki/machete_mlh_69/</t>
+          <t>https://motorring.ru/product/1025-mahovik-oblegchennyy-100detaley-215mm-dlya-shevrole-niva</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Machete MLH-69 4Ом</t>
+          <t>Маховик облегченный (вес около 4.6кг) 100деталей 215мм для Шевроле Нива</t>
         </is>
       </c>
       <c r="C1" t="n">
-        <v>3490</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.loudsound.ru/catalog/tvitery/tvitery_alphard_t_34/</t>
+          <t>https://www.ozon.ru/product/mahovik-2108-sport-oblegchennyy-100-detaley-879426533/</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alphard T-34 4Ом</t>
+          <t>Маховик 2108 спорт (облегченный) 100 Деталей</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5690</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://dbshop.ru/product/apocalypse_ap_m65an/</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2181-granta-standartnyy-1573733384/</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2181 Гранта стандартный</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4144</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://shop-bear.ru/catalog/akustika/vysokochastotnaya/hannibal-th-25g/</t>
+          <t>https://motorring.ru/product/8244-mahovik-oblegchennyy-100detaley-dlya-vaz-2108-21099</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hannibal TH-25G</t>
+          <t>Маховик облегченный (вес около 4 кг) 100деталей для ВАЗ 2108-21099, 2113-2115</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2990</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://shop-bear.ru/catalog/usiliteli/usilitel/avatar-ast-1200-1d/</t>
+          <t>https://motorring.ru/product/37234-mahovik-oblegchennyy-sceplenie-2123-100detaley-lada-vesta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avatar AST-1200.1D</t>
+          <t>Маховик 21176 облегченный 100деталей под сцепление 2123 (тяжелый) для Лада Веста</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10390</v>
+        <v>5490</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-sto-detaley-2123-16kl-tyazhelyy-4-6kg-1090108245/</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Маховик Сто Деталей 2123 16кл ТЯЖЕЛЫЙ 4,6кг</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2123-niva-shevrole-dlya-vaz-2101-2107-16v-oblegchennyy-100-detaley-v-1588977930/</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2123 Нива Шевроле для ВАЗ 2101-2107 16V облегченный 100 деталей в сборе балансрованный</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/31897-mahovik-oblegchennyy-100detaley-16v-2101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Маховик облегченный 100деталей для 16-клапанных ВАЗ 2101-2107, Лада 4х4</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2110-standartnyy-1573727887/</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2110 стандартный</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/37236-mahovik-oblegchennyy-stalnoy-100detaley-vaz-2110-2112</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Маховик стальной облегченный 100деталей для ВАЗ 2110-2112</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11790</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/31895-mahovik-oblegchennyy-100detaley-pod-sceplenie-2123-dlya-2101-4x4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Маховик облегченный 100деталей под сцепление 2123 для 16-клапанных ВАЗ 2101-2107, Лада 4х4</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2101-2107-16kl-oblegchennyy-balansirovannyy-852494579/</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2101-2107 16кл облегченный, балансированный</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/5803-mahovik-oblegchennyy-100detaley-dlya-vaz-2110-2112</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4 кг) 100деталей для ВАЗ 2110-2112</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/5807-mahovik-oblegchennyy-100detaley-pod-sceplenie-2123-dlya-2101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (тяжелый) 100деталей под сцепление 2123 для 16-клапанных ВАЗ 2101-2107, Лада 4х4</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/31898-mahovik-oblegchennyy-100detaley-8v-2101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Маховик облегченный 100деталей для 8-клапанных ВАЗ 2101-2107, Лада 4х4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/29296-mahovik-oblegchennyy-100detaley-turbo-pod-sceplenie-2110</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Маховик (вес около 4 кг) 100деталей Турбо под сцепление 2110 для ВАЗ 2108-21099, 2113-2115</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/40316-mahovik-oblegchennyy-stalnoy-100detaley-tros-kpp-granta</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Маховик облегченный стальной 100деталей для Лада Гранта, Гранта FL с тросовым приводом КПП</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12490</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/37235-mahovik-oblegchennyy-100detaley-lada-vesta</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Маховик 21176 облегченный 100деталей для Лада Веста</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-oblegchennyy-vaz-2101-2107-928074588/</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Маховик облегченный ВАЗ 2101 - 2107, Нива 21213</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2123-shevi-niva-oblegchennyy-balansirovannyy-852432193/</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2123 Шеви Нива облегченный, балансированный</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2181-trosovaya-kpp-oblegchennyy-100-detaley-v-sbore-balansirovannyy-1588981083/</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2181 тросовая КПП облегченный 100 деталей в сборе балансированный</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/5805-mahovik-oblegchennyy-4kg-sceplenie-2110-vaz-2108-21099-2113-2115</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4 кг) 100деталей под сцепление 2110 для ВАЗ 2108-21099, 2113-2115</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/14199-mahovik-oblegchennyy-100detaley-pod-trosovuyu-korobku</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 5.2кг) 100деталей под тросовую коробку передач для Лада Гранта</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2101-2107-niva-oblegchennyy-balansirovannyy-852409995/</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2101-2107, Нива облегченный, балансированный</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2108-pod-stseplenie-2110-oblegchennyy-balansirovannyy-855598916/</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2108 под сцепление 2110 облегченный , балансированный</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4233</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/1026-mahovik-oblegchennyy-100detaley-turbo-215mm-dlya-shevrole</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4.6кг) 100деталей Турбо 215мм для Шевроле Нива</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4490</v>
       </c>
     </row>
   </sheetData>
@@ -497,101 +818,511 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>AP-M65AN</t>
-        </is>
+      <c r="A1" t="n">
+        <v>163897</v>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://dbshop.ru/product/apocalypse_ap_m65an/</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
+          <t>https://motorring.ru/product/1026-mahovik-oblegchennyy-100detaley-turbo-215mm-dlya-shevrole</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4.6кг) 100деталей Турбо 215мм для Шевроле Нива</t>
+        </is>
+      </c>
+      <c r="D1" t="n">
+        <v>4490</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AST-1200.1D</t>
-        </is>
+      <c r="A2" t="n">
+        <v>163898</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://shop-bear.ru/catalog/usiliteli/usilitel/avatar-ast-1200-1d/</t>
+          <t>https://motorring.ru/product/29296-mahovik-oblegchennyy-100detaley-turbo-pod-sceplenie-2110</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Avatar AST-1200.1D</t>
+          <t>Маховик (вес около 4 кг) 100деталей Турбо под сцепление 2110 для ВАЗ 2108-21099, 2113-2115</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10390</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TH-25G</t>
-        </is>
+      <c r="A3" t="n">
+        <v>163891</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://shop-bear.ru/catalog/akustika/vysokochastotnaya/hannibal-th-25g/</t>
+          <t>https://motorring.ru/product/5807-mahovik-oblegchennyy-100detaley-pod-sceplenie-2123-dlya-2101</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hannibal TH-25G</t>
+          <t>Маховик облегченный (тяжелый) 100деталей под сцепление 2123 для 16-клапанных ВАЗ 2101-2107, Лада 4х4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2990</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MLH-69</t>
-        </is>
+      <c r="A4" t="n">
+        <v>163873</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.loudsound.ru/catalog/shirokopolosniki/machete_mlh_69/</t>
+          <t>https://motorring.ru/product/31898-mahovik-oblegchennyy-100detaley-8v-2101</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Machete MLH-69 4Ом</t>
+          <t>Маховик облегченный 100деталей для 8-клапанных ВАЗ 2101-2107, Лада 4х4</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3490</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T-34</t>
-        </is>
+      <c r="A5" t="n">
+        <v>163874</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.loudsound.ru/catalog/tvitery/tvitery_alphard_t_34/</t>
+          <t>https://motorring.ru/product/31897-mahovik-oblegchennyy-100detaley-16v-2101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alphard T-34 4Ом</t>
+          <t>Маховик облегченный 100деталей для 16-клапанных ВАЗ 2101-2107, Лада 4х4</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5690</v>
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>163875</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/8244-mahovik-oblegchennyy-100detaley-dlya-vaz-2108-21099</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4 кг) 100деталей для ВАЗ 2108-21099, 2113-2115</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>163876</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/5805-mahovik-oblegchennyy-4kg-sceplenie-2110-vaz-2108-21099-2113-2115</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4 кг) 100деталей под сцепление 2110 для ВАЗ 2108-21099, 2113-2115</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>163877</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/5803-mahovik-oblegchennyy-100detaley-dlya-vaz-2110-2112</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4 кг) 100деталей для ВАЗ 2110-2112</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>163879</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/31898-mahovik-oblegchennyy-100detaley-8v-2101</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Маховик облегченный 100деталей для 8-клапанных ВАЗ 2101-2107, Лада 4х4</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>163896</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/31895-mahovik-oblegchennyy-100detaley-pod-sceplenie-2123-dlya-2101-4x4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Маховик облегченный 100деталей под сцепление 2123 для 16-клапанных ВАЗ 2101-2107, Лада 4х4</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>163899</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/5807-mahovik-oblegchennyy-100detaley-pod-sceplenie-2123-dlya-2101</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (тяжелый) 100деталей под сцепление 2123 для 16-клапанных ВАЗ 2101-2107, Лада 4х4</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>163900</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/1025-mahovik-oblegchennyy-100detaley-215mm-dlya-shevrole-niva</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 4.6кг) 100деталей 215мм для Шевроле Нива</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>163842</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/14199-mahovik-oblegchennyy-100detaley-pod-trosovuyu-korobku</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Маховик облегченный (вес около 5.2кг) 100деталей под тросовую коробку передач для Лада Гранта</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>163893</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/37235-mahovik-oblegchennyy-100detaley-lada-vesta</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Маховик 21176 облегченный 100деталей для Лада Веста</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>163892</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/37234-mahovik-oblegchennyy-sceplenie-2123-100detaley-lada-vesta</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Маховик 21176 облегченный 100деталей под сцепление 2123 (тяжелый) для Лада Веста</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5490</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>163894</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/37236-mahovik-oblegchennyy-stalnoy-100detaley-vaz-2110-2112</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Маховик стальной облегченный 100деталей для ВАЗ 2110-2112</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11790</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>163895</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://motorring.ru/product/40316-mahovik-oblegchennyy-stalnoy-100detaley-tros-kpp-granta</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Маховик облегченный стальной 100деталей для Лада Гранта, Гранта FL с тросовым приводом КПП</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12490</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>163873</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-oblegchennyy-vaz-2101-2107-928074588/</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Маховик облегченный ВАЗ 2101 - 2107, Нива 21213</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>163874</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2101-2107-16kl-oblegchennyy-balansirovannyy-852494579/</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2101-2107 16кл облегченный, балансированный</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>163875</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-2108-sport-oblegchennyy-100-detaley-879426533/</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Маховик 2108 спорт (облегченный) 100 Деталей</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>163876</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2108-pod-stseplenie-2110-oblegchennyy-balansirovannyy-855598916/</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2108 под сцепление 2110 облегченный , балансированный</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4233</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>163877</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2110-standartnyy-1573727887/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2110 стандартный</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>163879</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2101-2107-niva-oblegchennyy-balansirovannyy-852409995/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2101-2107, Нива облегченный, балансированный</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>163896</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2123-niva-shevrole-dlya-vaz-2101-2107-16v-oblegchennyy-100-detaley-v-1588977930/</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2123 Нива Шевроле для ВАЗ 2101-2107 16V облегченный 100 деталей в сборе балансрованный</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>163899</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-sto-detaley-2123-16kl-tyazhelyy-4-6kg-1090108245/</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Маховик Сто Деталей 2123 16кл ТЯЖЕЛЫЙ 4,6кг</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>163900</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2123-shevi-niva-oblegchennyy-balansirovannyy-852432193/</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2123 Шеви Нива облегченный, балансированный</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>163842</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2181-granta-standartnyy-1573733384/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2181 Гранта стандартный</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>163893</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.ozon.ru/product/mahovik-vaz-2181-trosovaya-kpp-oblegchennyy-100-detaley-v-sbore-balansirovannyy-1588981083/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Маховик ВАЗ 2181 тросовая КПП облегченный 100 деталей в сборе балансированный</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>4472</v>
       </c>
     </row>
   </sheetData>
